--- a/Exam/gymtrackerpro/lib/controller/__tests__/it/workout-session-controller/updateWorkoutSessionWithExercises-it-form.xlsx
+++ b/Exam/gymtrackerpro/lib/controller/__tests__/it/workout-session-controller/updateWorkoutSessionWithExercises-it-form.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="75">
   <si>
     <t>Statement: updateWorkoutSessionWithExercises(workoutSessionId: string, data: UpdateWorkoutSessionInput, exercises: WorkoutSessionExerciseUpdateInput[]): Promise&lt;ActionResult&lt;WorkoutSessionWithExercises&gt;&gt; — validates both session and exercises with Zod, delegates to workoutSessionService.updateWorkoutSessionWithExercises(), and returns the reconciled session.</t>
   </si>
@@ -82,18 +82,19 @@
     <t>1</t>
   </si>
   <si>
-    <t xml:space="preserve">Member seeded via userService.createMember(). Exercise seeded via exerciseService.createExercise(). Session seeded via workoutSessionService.createWorkoutSession() with that exercise (WSE1).
-const data: UpdateWorkoutSessionInput = { duration: 90 }
-const exercises: WorkoutSessionExerciseUpdateInput[] = [{ id: WSE1.id, exerciseId: seededExercise.id, sets: 5, reps: 8, weight: 100 }]</t>
-  </si>
-  <si>
-    <t>updateWorkoutSessionWithExercises(seededSession.id, data, exercises)</t>
-  </si>
-  <si>
-    <t>{ success: true, data: { duration: 90, exercises: [{ sets: 5, reps: 8, weight: 100 }] } }</t>
-  </si>
-  <si>
-    <t>workout_sessions duration updated; WSE1 sets = 5, reps = 8, weight = 100</t>
+    <t xml:space="preserve">Member seeded via userService.createMember(). Exercise seeded via exerciseService.createExercise(). Session seeded via workoutSessionService.createWorkoutSession() with that exercise (sessionExercise).
+const inputId: string = seededSession.id
+const inputData: UpdateWorkoutSessionInput = { duration: 90 }
+const inputExercises: WorkoutSessionExerciseUpdateInput[] = [{ id: sessionExercise.id, exerciseId: seededExercise.id, sets: 5, reps: 8, weight: 100 }]</t>
+  </si>
+  <si>
+    <t>updateWorkoutSessionWithExercises(inputId, inputData, inputExercises)</t>
+  </si>
+  <si>
+    <t>{ success: true, data: { duration: 90, exercises: [{ id: sessionExercise.id, sets: 5, reps: 8, weight: 100 }] } }</t>
+  </si>
+  <si>
+    <t>workout_sessions duration updated; sessionExercise sets = 5, reps = 8, weight = 100</t>
   </si>
   <si>
     <t>Passed</t>
@@ -103,10 +104,11 @@
   </si>
   <si>
     <t xml:space="preserve">Member seeded via userService.createMember(). Exercise seeded via exerciseService.createExercise(). Session seeded via workoutSessionService.createWorkoutSession().
-const exercises: WorkoutSessionExerciseUpdateInput[] = []</t>
-  </si>
-  <si>
-    <t>updateWorkoutSessionWithExercises(seededSession.id, {}, exercises)</t>
+const inputId: string = seededSession.id
+const inputExercises: WorkoutSessionExerciseUpdateInput[] = []</t>
+  </si>
+  <si>
+    <t>updateWorkoutSessionWithExercises(inputId, {}, inputExercises)</t>
   </si>
   <si>
     <t>{ success: false, message: defined non-empty string ("At least one exercise is required") }</t>
@@ -118,44 +120,98 @@
     <t>3</t>
   </si>
   <si>
+    <t xml:space="preserve">Empty database.
+const inputId: string = "00000000-0000-0000-0000-000000000000"
+const inputData = { date: "not-a-date" } as unknown as UpdateWorkoutSessionInput
+const inputExercises: WorkoutSessionExerciseUpdateInput[] = []</t>
+  </si>
+  <si>
+    <t>{ success: false, message: "Validation failed", errors: { date: defined } }</t>
+  </si>
+  <si>
+    <t>No change</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
     <t xml:space="preserve">Exercise seeded via exerciseService.createExercise(). No session in database.
-const exercises: WorkoutSessionExerciseUpdateInput[] = [{ exerciseId: seededExercise.id, sets: 3, reps: 10, weight: 50 }]</t>
-  </si>
-  <si>
-    <t>updateWorkoutSessionWithExercises("00000000-0000-0000-0000-000000000000", {}, exercises)</t>
+const inputId: string = "00000000-0000-0000-0000-000000000000"
+const inputExercises: WorkoutSessionExerciseUpdateInput[] = [{ exerciseId: seededExercise.id, sets: 3, reps: 10, weight: 50 }]</t>
   </si>
   <si>
     <t>{ success: false, message: defined non-empty string (NotFoundError message) }</t>
   </si>
   <si>
-    <t>No change</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Empty database.
-const input = { date: "not-a-date" } as unknown as UpdateWorkoutSessionInput
-const exercises: WorkoutSessionExerciseUpdateInput[] = []</t>
-  </si>
-  <si>
-    <t>updateWorkoutSessionWithExercises("any-id", input, exercises)</t>
-  </si>
-  <si>
-    <t>{ success: false, message: "Validation failed", errors: { date: defined } }</t>
-  </si>
-  <si>
     <t>5</t>
   </si>
   <si>
-    <t xml:space="preserve">Member seeded via userService.createMember(). Two exercises seeded via exerciseService.createExercise(). Session seeded via workoutSessionService.createWorkoutSession() with both exercises (WSE1, WSE2). Third exercise seeded.
-const exercises: WorkoutSessionExerciseUpdateInput[] = [{ id: WSE1.id, exerciseId: exercise1.id, sets: 4, reps: 12, weight: 60 }, { exerciseId: exercise3.id, sets: 3, reps: 10, weight: 40 }] — exercise2 omitted</t>
-  </si>
-  <si>
-    <t>{ success: true, data: { exercises: [length 2, WSE1 updated, exercise3 present, exercise2 absent] } }</t>
-  </si>
-  <si>
-    <t>WSE1 sets = 4; WSE2 row removed; new WSE row for exercise3 created</t>
+    <t xml:space="preserve">Member seeded via userService.createMember(). Two exercises seeded: benchPressExercise, deadliftExercise. Session seeded via workoutSessionService.createWorkoutSession() with both exercises (benchPressEntry, deadliftEntry).
+const inputId: string = seededSession.id
+const inputExercises: WorkoutSessionExerciseUpdateInput[] = [{ id: benchPressEntry.id, exerciseId: benchPressExercise.id, sets: 3, reps: 10, weight: 50 }] (deadliftExercise omitted)</t>
+  </si>
+  <si>
+    <t>{ success: true, data: { exercises: [length 1, benchPressEntry present] } }</t>
+  </si>
+  <si>
+    <t>deadliftEntry row removed; benchPressEntry row retained</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Member seeded via userService.createMember(). Exercise seeded via exerciseService.createExercise(). Session seeded via workoutSessionService.createWorkoutSession() with that exercise (sessionExercise).
+const inputId: string = seededSession.id
+const inputExercises: WorkoutSessionExerciseUpdateInput[] = [{ id: sessionExercise.id, exerciseId: seededExercise.id, sets: 5, reps: 8, weight: 100 }]</t>
+  </si>
+  <si>
+    <t>{ success: true, data: { exercises: [{ id: sessionExercise.id, sets: 5, reps: 8, weight: 100 }] } }</t>
+  </si>
+  <si>
+    <t>sessionExercise sets = 5, reps = 8, weight = 100</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Member seeded via userService.createMember(). Two exercises seeded: benchPressExercise, deadliftExercise. Session seeded via workoutSessionService.createWorkoutSession() with benchPressExercise only (benchPressEntry).
+const inputId: string = seededSession.id
+const inputExercises: WorkoutSessionExerciseUpdateInput[] = [{ id: benchPressEntry.id, exerciseId: benchPressExercise.id, sets: 3, reps: 10, weight: 50 }, { exerciseId: deadliftExercise.id, sets: 2, reps: 15, weight: 20 }]</t>
+  </si>
+  <si>
+    <t>{ success: true, data: { exercises: [length 2, benchPressEntry present, deadliftExercise new entry present] } }</t>
+  </si>
+  <si>
+    <t>benchPressEntry row retained; new workout_session_exercises row for deadliftExercise created</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Member seeded via userService.createMember(). Three exercises seeded: benchPressExercise, deadliftExercise, squatExercise. Session seeded via workoutSessionService.createWorkoutSession() with benchPressExercise and deadliftExercise (benchPressEntry, deadliftEntry).
+const inputId: string = seededSession.id
+const inputExercises: WorkoutSessionExerciseUpdateInput[] = [{ id: benchPressEntry.id, exerciseId: benchPressExercise.id, sets: 4, reps: 12, weight: 60 }, { exerciseId: squatExercise.id, sets: 3, reps: 10, weight: 40 }] (deadliftExercise omitted)</t>
+  </si>
+  <si>
+    <t>{ success: true, data: { exercises: [length 2, benchPressEntry sets = 4, squatExercise entry present, deadliftEntry absent] } }</t>
+  </si>
+  <si>
+    <t>benchPressEntry sets = 4; deadliftEntry row removed; new row for squatExercise created</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Member seeded via userService.createMember(). Exercise seeded via exerciseService.createExercise(). Session seeded via workoutSessionService.createWorkoutSession() with that exercise (sessionExercise). Prior call to updateWorkoutSessionWithExercises() with empty exercises array executed and returned { success: false }.
+const inputId: string = seededSession.id
+const inputData: UpdateWorkoutSessionInput = { duration: 90 }
+const inputExercises: WorkoutSessionExerciseUpdateInput[] = [{ id: sessionExercise.id, exerciseId: seededExercise.id, sets: 3, reps: 10, weight: 50 }]</t>
+  </si>
+  <si>
+    <t>{ success: true, data: { duration: 90 } }</t>
+  </si>
+  <si>
+    <t>workout_sessions duration updated to 90; sessionExercise row unchanged</t>
   </si>
   <si>
     <t>Testing</t>
@@ -847,12 +903,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="14" customWidth="1"/>
-    <col min="3" max="5" width="80" customWidth="1"/>
-    <col min="6" max="6" width="76" customWidth="1"/>
+    <col min="3" max="3" width="80" customWidth="1"/>
+    <col min="4" max="4" width="73" customWidth="1"/>
+    <col min="5" max="6" width="80" customWidth="1"/>
     <col min="7" max="7" width="17" customWidth="1"/>
   </cols>
   <sheetData>
@@ -879,7 +936,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" ht="95" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" ht="110" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -925,7 +982,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" ht="50" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" ht="65" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -936,36 +993,36 @@
         <v>33</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="5" ht="50" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" ht="65" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>1</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="F5" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>26</v>
@@ -976,21 +1033,113 @@
         <v>1</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>29</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" ht="95" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="C7" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="D7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" ht="110" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" ht="125" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" ht="125" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G10" s="6" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1019,17 +1168,17 @@
         <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
@@ -1041,40 +1190,40 @@
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -1082,40 +1231,40 @@
         <v>1</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="C6" s="1">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D6" s="1">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E6" s="1">
         <v>0</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="J6" s="1">
         <v>0</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
